--- a/Cochin-March-2026.xlsx
+++ b/Cochin-March-2026.xlsx
@@ -115,13 +115,13 @@
     <t>KL07DF3416</t>
   </si>
   <si>
-    <t>Dzire</t>
-  </si>
-  <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Citroen</t>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>URBANIA</t>
